--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487566_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487566_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5015</v>
+        <v>6.0192</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7507</v>
+        <v>5.5625</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7508</v>
+        <v>0.4567</v>
       </c>
       <c r="G2" t="n">
         <v>2.7922</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2968</v>
+        <v>-0.1854</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0612</v>
+        <v>-0.2494</v>
       </c>
       <c r="U2" t="n">
-        <v>0.358</v>
+        <v>0.064</v>
       </c>
       <c r="V2" t="n">
         <v>2.4332</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6201</v>
+        <v>4.6468</v>
       </c>
       <c r="E3" t="n">
         <v>3.2744</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3457</v>
+        <v>1.3724</v>
       </c>
       <c r="G3" t="n">
         <v>2.031</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8603</v>
+        <v>-0.8335</v>
       </c>
       <c r="T3" t="n">
         <v>-0.6358</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2245</v>
+        <v>-0.1978</v>
       </c>
       <c r="V3" t="n">
         <v>1.8825</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8182</v>
+        <v>3.6801</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1431</v>
+        <v>5.9783</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3249</v>
+        <v>-2.2981</v>
       </c>
       <c r="G4" t="n">
         <v>5.5393</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9342</v>
+        <v>-1.0723</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7227</v>
+        <v>-0.8875</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2115</v>
+        <v>-0.1848</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1578</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5958</v>
+        <v>1.9309</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7843</v>
+        <v>1.2531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8115</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.5407</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6108</v>
+        <v>-0.2757</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5346</v>
+        <v>-0.0659</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0762</v>
+        <v>-0.2098</v>
       </c>
       <c r="V5" t="n">
         <v>0.6659</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3669</v>
+        <v>1.7906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1165</v>
+        <v>1.2613</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2505</v>
+        <v>0.5294</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7742</v>
+        <v>0.7657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1127</v>
+        <v>0.261</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6615</v>
+        <v>0.5046</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9106</v>
+        <v>1.9729</v>
       </c>
       <c r="K6" t="n">
-        <v>1.674</v>
+        <v>1.3474</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2366</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1364</v>
+        <v>-1.2073</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5613</v>
+        <v>-1.0864</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4249</v>
+        <v>-0.1209</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0743</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.111</v>
+        <v>-0.7116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0367</v>
+        <v>0.1698</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3408</v>
+        <v>1.6831</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1589</v>
+        <v>0.2188</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1819</v>
+        <v>1.4643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7657</v>
+        <v>1.7742</v>
       </c>
       <c r="H7" t="n">
-        <v>0.261</v>
+        <v>0.1127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5046</v>
+        <v>1.6615</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9729</v>
+        <v>2.9106</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3474</v>
+        <v>1.674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.2366</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2073</v>
+        <v>-1.1364</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0864</v>
+        <v>-1.5613</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1209</v>
+        <v>0.4249</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9917</v>
+        <v>-0.7581</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-1.0087</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1777</v>
+        <v>0.2506</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0161</v>
+        <v>0.3026</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4024</v>
+        <v>-2.2572</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3863</v>
+        <v>2.5598</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0479</v>
+        <v>-3.7476</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1794</v>
+        <v>-2.4336</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2273</v>
+        <v>-1.314</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.601</v>
+        <v>-4.0278</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0408</v>
+        <v>-2.0263</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6418</v>
+        <v>-2.0015</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5531</v>
+        <v>0.2802</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1385</v>
+        <v>-0.4073</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4145</v>
+        <v>0.6874</v>
       </c>
       <c r="P8" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4178</v>
+        <v>0.4787</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4527</v>
+        <v>-0.2341</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0349</v>
+        <v>0.7128</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9412</v>
+        <v>2.9839</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5507</v>
+        <v>2.9839</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4049</v>
+        <v>0.0033</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1548</v>
+        <v>0.3361</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5598</v>
+        <v>-0.3328</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7476</v>
+        <v>-0.0479</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4336</v>
+        <v>0.1794</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.314</v>
+        <v>-0.2273</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.0278</v>
+        <v>-0.601</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0263</v>
+        <v>0.0408</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0015</v>
+        <v>-0.6418</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2802</v>
+        <v>0.5531</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4073</v>
+        <v>0.1385</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6874</v>
+        <v>0.4145</v>
       </c>
       <c r="P9" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.4049</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>0.3864</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7128</v>
+        <v>0.0185</v>
       </c>
       <c r="V9" t="n">
-        <v>2.9839</v>
+        <v>-0.9412</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9839</v>
+        <v>0.5507</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9439</v>
+        <v>-0.6263</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9351</v>
+        <v>-0.6711</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2781</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8248</v>
+        <v>-0.5073</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5346</v>
+        <v>-0.2705</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2902</v>
+        <v>-0.2367</v>
       </c>
       <c r="V10" t="n">
         <v>0.5507</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4463</v>
+        <v>-1.0218</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0006</v>
+        <v>1.2647</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4469</v>
+        <v>-2.2865</v>
       </c>
       <c r="G11" t="n">
         <v>0.0728</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0858</v>
+        <v>-0.6614</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4158</v>
+        <v>-0.1517</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.67</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4526</v>
+        <v>-1.9662</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9305</v>
+        <v>-2.0164</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4779</v>
+        <v>0.0502</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8426</v>
@@ -1390,13 +1390,13 @@
         <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1181</v>
+        <v>-0.6317</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2088</v>
+        <v>-0.2947</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0907</v>
+        <v>-0.337</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2754</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3115</v>
+        <v>-4.3382</v>
       </c>
       <c r="E13" t="n">
         <v>-4.8666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5551</v>
+        <v>0.5283</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9589</v>
@@ -1468,13 +1468,13 @@
         <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0772</v>
+        <v>-0.104</v>
       </c>
       <c r="T13" t="n">
         <v>-0.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1427</v>
+        <v>0.116</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8837</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.51</v>
+        <v>12.1041</v>
       </c>
       <c r="E14" t="n">
-        <v>8.7439</v>
+        <v>9.337900000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7664</v>
+        <v>2.7663</v>
       </c>
       <c r="G14" t="n">
         <v>5.640800000000002</v>
@@ -1546,13 +1546,13 @@
         <v>14.6886</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.2815</v>
+        <v>-4.687600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.937499999999999</v>
+        <v>-4.3435</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3441000000000001</v>
+        <v>-0.3440000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.3169</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2758</v>
+        <v>2.3457</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0916</v>
+        <v>4.7353</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8158</v>
+        <v>-2.3896</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6397</v>
+        <v>2.5524</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5886</v>
+        <v>2.9762</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0512</v>
+        <v>-0.4238</v>
       </c>
       <c r="J15" t="n">
-        <v>3.496</v>
+        <v>4.9524</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3343</v>
+        <v>3.6543</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1617</v>
+        <v>1.2981</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8563</v>
+        <v>-2.4</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7458</v>
+        <v>-0.6781</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1105</v>
+        <v>-1.7219</v>
       </c>
       <c r="P15" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5981</v>
+        <v>1.147</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2408</v>
+        <v>0.1159</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3573</v>
+        <v>1.0312</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1578</v>
+        <v>-1.5495</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6659</v>
+        <v>-0.3329</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.492</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4876</v>
+        <v>2.0986</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6524</v>
+        <v>2.4477</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1649</v>
+        <v>-0.3492</v>
       </c>
       <c r="G16" t="n">
         <v>1.8022</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0689</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1764</v>
+        <v>-0.0282</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8924</v>
+        <v>0.7081</v>
       </c>
       <c r="V16" t="n">
         <v>3.9252</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2793</v>
+        <v>1.9085</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4283</v>
+        <v>2.4543</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.149</v>
+        <v>-0.5457</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5524</v>
+        <v>2.6397</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9762</v>
+        <v>2.5886</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4238</v>
+        <v>0.0512</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9524</v>
+        <v>3.496</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6543</v>
+        <v>3.3343</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2981</v>
+        <v>0.1617</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4</v>
+        <v>-0.8563</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6781</v>
+        <v>-0.7458</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7219</v>
+        <v>-0.1105</v>
       </c>
       <c r="P17" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0806</v>
+        <v>1.2308</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1911</v>
+        <v>0.6034</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2717</v>
+        <v>0.6274</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5495</v>
+        <v>-2.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>-0.6659</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1714</v>
+        <v>0.6513</v>
       </c>
       <c r="E18" t="n">
-        <v>1.915</v>
+        <v>-0.0146</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7436</v>
+        <v>0.6659</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6604</v>
+        <v>0.13</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1987</v>
+        <v>-0.1429</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8591</v>
+        <v>0.2729</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7417</v>
+        <v>0.0612</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4903</v>
+        <v>0.0612</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7486</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4021</v>
+        <v>0.0687</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2916</v>
+        <v>-0.2042</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1105</v>
+        <v>0.2729</v>
       </c>
       <c r="P18" t="n">
         <v>0.7834</v>
@@ -1858,28 +1858,28 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8744</v>
+        <v>0.0132</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1733</v>
+        <v>-0.0759</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.0891</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4955</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.117</v>
+        <v>1.0963</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6124000000000001</v>
+        <v>-0.5565</v>
       </c>
       <c r="G19" t="n">
-        <v>0.13</v>
+        <v>-0.6604</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1429</v>
+        <v>0.1987</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2729</v>
+        <v>-0.8591</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0612</v>
+        <v>0.7417</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0612</v>
+        <v>1.4903</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.7486</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0687</v>
+        <v>-1.4021</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2042</v>
+        <v>-1.2916</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2729</v>
+        <v>-0.1105</v>
       </c>
       <c r="P19" t="n">
         <v>0.7834</v>
@@ -1936,22 +1936,22 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1426</v>
+        <v>1.2429</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1782</v>
+        <v>0.3546</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0356</v>
+        <v>0.8882</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4473</v>
+        <v>-2.5724</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2732</v>
+        <v>-1.4545</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1741</v>
+        <v>-1.1179</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7308</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5575</v>
+        <v>0.3174</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1704</v>
+        <v>-0.3517</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6129</v>
+        <v>0.6692</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5507</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ALIK</t>
+          <t>M. TRAORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5766</v>
+        <v>-3.3407</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4095</v>
+        <v>-2.7362</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1671</v>
+        <v>-0.6044</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6843</v>
+        <v>-2.3966</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9371</v>
+        <v>-1.8415</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7471</v>
+        <v>-0.5551</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5572</v>
+        <v>-0.2059</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5976</v>
+        <v>-1.504</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0404</v>
+        <v>1.2981</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1271</v>
+        <v>-2.1906</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3396</v>
+        <v>-0.3375</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7875</v>
+        <v>-1.8532</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5996</v>
+        <v>0.5017</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1476</v>
+        <v>-0.1053</v>
       </c>
       <c r="U21" t="n">
-        <v>0.452</v>
+        <v>0.607</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.492</v>
+        <v>1.492</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. TRAORE</t>
+          <t>J. ALIK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3935</v>
+        <v>-3.8126</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7596</v>
+        <v>-1.5119</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.634</v>
+        <v>-2.3007</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3966</v>
+        <v>-2.6843</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8415</v>
+        <v>-1.9371</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5551</v>
+        <v>-0.7471</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2059</v>
+        <v>-1.5572</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.504</v>
+        <v>-1.5976</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2981</v>
+        <v>0.0404</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1906</v>
+        <v>-1.1271</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3375</v>
+        <v>-0.3396</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8532</v>
+        <v>-0.7875</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5512</v>
+        <v>0.3636</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1286</v>
+        <v>0.0453</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5774</v>
+        <v>0.3183</v>
       </c>
       <c r="V22" t="n">
-        <v>1.492</v>
+        <v>-1.492</v>
       </c>
       <c r="W22" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.802099999999999</v>
+        <v>-8.646100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.2943</v>
+        <v>-7.7826</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5078</v>
+        <v>-0.8635</v>
       </c>
       <c r="G23" t="n">
         <v>-4.293</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6889</v>
+        <v>0.4671</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7258</v>
+        <v>-0.2141</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0369</v>
+        <v>0.6812</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8825</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.5099</v>
+        <v>-10.8279</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.766300000000001</v>
+        <v>-2.7662</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.7439</v>
+        <v>-8.0616</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6408</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6822</v>
+        <v>1.682200000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-7.3229</v>
       </c>
       <c r="J24" t="n">
-        <v>6.609300000000001</v>
+        <v>6.609299999999999</v>
       </c>
       <c r="K24" t="n">
         <v>6.7651</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1557000000000002</v>
+        <v>-0.1557000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-12.2503</v>
@@ -2326,13 +2326,13 @@
         <v>6.8545</v>
       </c>
       <c r="S24" t="n">
-        <v>5.2814</v>
+        <v>5.9636</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3439999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="U24" t="n">
-        <v>4.9373</v>
+        <v>5.6197</v>
       </c>
       <c r="V24" t="n">
         <v>-3.3168</v>
